--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20222.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -85,82 +85,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>NAMORADO</t>
+  </si>
+  <si>
+    <t>QUIRIZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
-    <t>ARROYO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>NIEVES</t>
   </si>
   <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
+    <t>LUZ ESTRELLA</t>
+  </si>
+  <si>
+    <t>MONICA</t>
   </si>
   <si>
     <t>CANDIDO</t>
-  </si>
-  <si>
-    <t>CRISTIAN ARTURO</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>ANGELES NAHOMI</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
   </si>
 </sst>
 </file>
@@ -779,16 +728,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>86.20999999999999</v>
+      </c>
+      <c r="H3">
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -802,16 +754,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>91.67</v>
+      </c>
+      <c r="H4">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -825,16 +780,19 @@
         <v>32</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>32</v>
       </c>
-      <c r="E5">
-        <v>32</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>8.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -962,16 +920,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>75.86</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -988,16 +946,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>83.33</v>
+        <v>94.44</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1023,7 +981,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1085,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1117,22 +1075,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920163</v>
+        <v>20330051920174</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1140,22 +1098,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920171</v>
+        <v>20330051920178</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1169,10 +1127,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1181,144 +1139,6 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920172</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920174</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920178</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920157</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920162</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920182</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20222.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -85,28 +85,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>NAMORADO</t>
-  </si>
-  <si>
-    <t>QUIRIZ</t>
-  </si>
-  <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>NIEVES</t>
-  </si>
-  <si>
-    <t>LUZ ESTRELLA</t>
-  </si>
-  <si>
-    <t>MONICA</t>
   </si>
   <si>
     <t>CANDIDO</t>
@@ -754,19 +736,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -806,16 +788,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H6">
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -946,13 +931,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>94.44</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>8.6</v>
@@ -998,13 +983,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H6">
         <v>7</v>
@@ -1043,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1075,70 +1060,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920174</v>
+        <v>21330051920176</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920178</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920176</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20222.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,15 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>CANDIDO</t>
   </si>
 </sst>
 </file>
@@ -687,16 +678,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80.65000000000001</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -879,16 +873,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>74.19</v>
+        <v>93.55</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1028,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1058,29 +1052,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920176</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20222.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -83,6 +83,24 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>MEILYN ADABEL</t>
   </si>
 </sst>
 </file>
@@ -678,19 +696,19 @@
         <v>31</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>5</v>
       </c>
-      <c r="E2">
-        <v>6</v>
-      </c>
       <c r="F2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>80.65000000000001</v>
+        <v>83.87</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -808,16 +826,19 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>87.09999999999999</v>
+      </c>
+      <c r="H7">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -873,16 +894,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>93.55</v>
+        <v>83.87</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1003,16 +1024,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -1022,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1052,6 +1073,52 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920164</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920148</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20222.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,24 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
   </si>
 </sst>
 </file>
@@ -894,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>83.87</v>
+        <v>96.77</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -920,16 +902,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>86.20999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -955,7 +937,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -981,7 +963,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -998,16 +980,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>71.43000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1024,16 +1006,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>87.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -1043,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1073,52 +1055,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920164</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920148</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
